--- a/raw-data/VFT Compiled data 2025/CH-25-all.xlsx
+++ b/raw-data/VFT Compiled data 2025/CH-25-all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\VFT Compiled data 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B367D2-2BDA-4C67-AD04-8D10FCFC14B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDD2601-8615-44C0-BFCC-C00818C5BA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22943" yWindow="1365" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11438" yWindow="0" windowWidth="11684" windowHeight="13763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CH" sheetId="1" r:id="rId1"/>
